--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -396,16 +396,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
-      </c>
-      <c r="C2">
-        <v>200</v>
+        <v>https://aiboren.jp/shisetsu/</v>
+      </c>
+      <c r="C2" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D2" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="3">
@@ -413,13 +413,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="4">
@@ -427,13 +427,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -455,7 +455,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,7 +483,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C91">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,10 +1659,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C92">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D92" t="str">
         <v>data/services.js</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -3525,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3543,13 +3543,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="B2" t="str">
-        <v>【準備中】令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C2" t="str">
-        <v>令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3557,98 +3557,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="B3" t="str">
-        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
+        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C3" t="str">
-        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
+        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D3" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
-      </c>
-      <c r="B4" t="str">
-        <v>就学援助（未来まなび応援金）｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C4" t="str">
-        <v>未来まなび応援金（就学援助制度）｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D4" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
-      </c>
-      <c r="B5" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="C5" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="D5" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="C6" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="D6" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
-      </c>
-      <c r="B7" t="str">
-        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C7" t="str">
-        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D7" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
-      </c>
-      <c r="B8" t="str">
-        <v>おたふくかぜ予防接種の費用助成(任意予防接種)｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C8" t="str">
-        <v>おたふくかぜ予防接種(任意予防接種)｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D8" t="str">
         <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3678,10 +3608,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
       </c>
       <c r="E2" t="str">
-        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
+        <v>第12次名古屋市交通安全計画</v>
       </c>
     </row>
     <row r="3">
@@ -3695,10 +3625,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053423.html</v>
       </c>
       <c r="E3" t="str">
-        <v>空き家情報冊子の無償提供者の募集</v>
+        <v>令和8年度名古屋市交通安全実施計画</v>
       </c>
     </row>
     <row r="4">
@@ -3712,10 +3642,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
       </c>
       <c r="E4" t="str">
-        <v>熱田区の消防団について</v>
+        <v>空き家情報冊子の無償提供者の募集</v>
       </c>
     </row>
     <row r="5">
@@ -3729,10 +3659,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
       </c>
       <c r="E5" t="str">
-        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
+        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
       </c>
     </row>
     <row r="6">
@@ -3746,10 +3676,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
       </c>
       <c r="E6" t="str">
-        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
+        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
       </c>
     </row>
     <row r="7">
@@ -3763,10 +3693,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
       </c>
       <c r="E7" t="str">
-        <v>港土木だより第29号</v>
+        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
       </c>
     </row>
     <row r="8">
@@ -3780,10 +3710,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
       </c>
       <c r="E8" t="str">
-        <v>公園配置図</v>
+        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
       </c>
     </row>
     <row r="9">
@@ -3797,10 +3727,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
       </c>
       <c r="E9" t="str">
-        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
+        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
       </c>
     </row>
     <row r="10">
@@ -3814,10 +3744,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
       </c>
       <c r="E10" t="str">
-        <v>公園でスポーツ教室を開催したい</v>
+        <v>港土木だより第29号</v>
       </c>
     </row>
     <row r="11">
@@ -3831,27 +3761,27 @@
         <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
       </c>
       <c r="E11" t="str">
-        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
+        <v>公園配置図</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C12" t="str">
-        <v>🔁 変更</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1010455/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
       </c>
       <c r="E12" t="str">
-        <v>道路資産の有効活用の取組み → 道路・公園資産の有効活用の取組み</v>
+        <v>令和8年度 教育委員会9月定例会</v>
       </c>
     </row>
     <row r="13">
@@ -3865,10 +3795,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
       </c>
       <c r="E13" t="str">
-        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
+        <v>内山保育園の改築について</v>
       </c>
     </row>
     <row r="14">
@@ -3882,10 +3812,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
       </c>
       <c r="E14" t="str">
-        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
+        <v>公立保育所等の整備</v>
       </c>
     </row>
     <row r="15">
@@ -3896,13 +3826,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C15" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
       </c>
       <c r="E15" t="str">
-        <v>こどもホスピス支援事業</v>
+        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
       </c>
     </row>
     <row r="16">
@@ -3916,10 +3846,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
       </c>
       <c r="E16" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
       </c>
     </row>
     <row r="17">
@@ -3933,27 +3863,27 @@
         <v>➖ 削除</v>
       </c>
       <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
       </c>
       <c r="E17" t="str">
-        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>こどもホスピス支援事業</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>健康・医療・福祉</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C18" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016555/1037469.html</v>
       </c>
       <c r="E18" t="str">
-        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+        <v>令和8年度アディクション・セッション「だれでもなる依存症 ーそれぞれの回復メッセージー」</v>
       </c>
     </row>
     <row r="19">
@@ -3964,110 +3894,25 @@
         <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C19" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
       </c>
       <c r="E19" t="str">
-        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C20" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
-      </c>
-      <c r="E20" t="str">
-        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C21" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
-      </c>
-      <c r="E21" t="str">
         <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C22" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D22" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
-      </c>
-      <c r="E22" t="str">
-        <v>令和8年度「衛研だより」</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C23" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D23" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C24" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D24" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
-      </c>
-      <c r="E24" t="str">
-        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8077,9 +7922,480 @@
         <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
       </c>
     </row>
+    <row r="187">
+      <c r="B187" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C187" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D187" t="str">
+        <v>https://aiboren.jp/shisetsu/</v>
+      </c>
+      <c r="E187" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F187" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C188" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D188" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+      </c>
+      <c r="F188" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G188" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H188" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C189" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D189" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+      </c>
+      <c r="F189" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G189" t="str">
+        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H189" t="str">
+        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C190" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I190" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J190" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K190" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L190" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
+      </c>
+      <c r="M190" t="str">
+        <v>第12次名古屋市交通安全計画</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C191" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I191" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J191" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K191" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L191" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053423.html</v>
+      </c>
+      <c r="M191" t="str">
+        <v>令和8年度名古屋市交通安全実施計画</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C192" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I192" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J192" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K192" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L192" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
+      </c>
+      <c r="M192" t="str">
+        <v>空き家情報冊子の無償提供者の募集</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C193" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I193" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K193" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L193" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
+      </c>
+      <c r="M193" t="str">
+        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C194" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I194" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K194" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L194" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
+      </c>
+      <c r="M194" t="str">
+        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C195" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I195" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K195" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L195" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
+      </c>
+      <c r="M195" t="str">
+        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C196" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I196" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K196" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L196" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
+      </c>
+      <c r="M196" t="str">
+        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C197" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I197" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K197" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L197" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
+      </c>
+      <c r="M197" t="str">
+        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C198" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I198" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K198" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L198" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
+      </c>
+      <c r="M198" t="str">
+        <v>港土木だより第29号</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C199" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I199" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K199" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L199" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
+      </c>
+      <c r="M199" t="str">
+        <v>公園配置図</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C200" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I200" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K200" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L200" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
+      </c>
+      <c r="M200" t="str">
+        <v>令和8年度 教育委員会9月定例会</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C201" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I201" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K201" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L201" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
+      </c>
+      <c r="M201" t="str">
+        <v>内山保育園の改築について</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C202" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I202" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K202" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L202" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
+      </c>
+      <c r="M202" t="str">
+        <v>公立保育所等の整備</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C203" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I203" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K203" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L203" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
+      </c>
+      <c r="M203" t="str">
+        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C204" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I204" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K204" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L204" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
+      </c>
+      <c r="M204" t="str">
+        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C205" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I205" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K205" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L205" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
+      </c>
+      <c r="M205" t="str">
+        <v>こどもホスピス支援事業</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C206" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I206" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K206" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L206" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016555/1037469.html</v>
+      </c>
+      <c r="M206" t="str">
+        <v>令和8年度アディクション・セッション「だれでもなる依存症 ーそれぞれの回復メッセージー」</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C207" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I207" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K207" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L207" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="M207" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -396,16 +396,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B2" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
-      </c>
-      <c r="C2" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
       </c>
       <c r="D2" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="3">
@@ -413,13 +413,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="4">
@@ -427,13 +427,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -455,7 +455,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,7 +483,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C91">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,10 +1659,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C92">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D92" t="str">
         <v>data/services.js</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -3525,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3543,13 +3543,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="B2" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="C2" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3557,21 +3557,49 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="B3" t="str">
-        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C3" t="str">
-        <v>防災・危機管理（防災ポータル）｜名古屋市公式ウェブサイト</v>
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D3" t="str">
         <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+      </c>
+      <c r="B4" t="str">
+        <v>高齢者肺炎球菌(定期予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C4" t="str">
+        <v>高齢者肺炎球菌予防接種(定期予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D4" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="B5" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C5" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D5" t="str">
+        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3608,10 +3636,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
       </c>
       <c r="E2" t="str">
-        <v>第12次名古屋市交通安全計画</v>
+        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
       </c>
     </row>
     <row r="3">
@@ -3622,7 +3650,7 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D3" t="str">
         <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053423.html</v>
@@ -3633,36 +3661,36 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C4" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
       </c>
       <c r="E4" t="str">
-        <v>空き家情報冊子の無償提供者の募集</v>
+        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
       </c>
       <c r="E5" t="str">
-        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
+        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
       </c>
     </row>
     <row r="6">
@@ -3676,10 +3704,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
       </c>
       <c r="E6" t="str">
-        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
+        <v>愛知県勤労者スポーツフェスティバル</v>
       </c>
     </row>
     <row r="7">
@@ -3690,13 +3718,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C7" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
       </c>
       <c r="E7" t="str">
-        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
+        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
       </c>
     </row>
     <row r="8">
@@ -3707,13 +3735,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
       </c>
       <c r="E8" t="str">
-        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
+        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
       </c>
     </row>
     <row r="9">
@@ -3727,44 +3755,44 @@
         <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
       </c>
       <c r="E9" t="str">
-        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
+        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C10" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
       </c>
       <c r="E10" t="str">
-        <v>港土木だより第29号</v>
+        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1053964.html</v>
       </c>
       <c r="E11" t="str">
-        <v>公園配置図</v>
+        <v>こども性暴力防止法</v>
       </c>
     </row>
     <row r="12">
@@ -3778,10 +3806,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
       </c>
       <c r="E12" t="str">
-        <v>令和8年度 教育委員会9月定例会</v>
+        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
       </c>
     </row>
     <row r="13">
@@ -3792,13 +3820,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C13" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
       </c>
       <c r="E13" t="str">
-        <v>内山保育園の改築について</v>
+        <v>令和8年度 教育委員会9月定例会</v>
       </c>
     </row>
     <row r="14">
@@ -3809,13 +3837,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C14" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
       </c>
       <c r="E14" t="str">
-        <v>公立保育所等の整備</v>
+        <v>内山保育園の改築について</v>
       </c>
     </row>
     <row r="15">
@@ -3829,44 +3857,44 @@
         <v>➖ 削除</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
       </c>
       <c r="E15" t="str">
-        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
+        <v>公立保育所等の整備</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>健康・医療・福祉</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C16" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
       </c>
       <c r="E16" t="str">
-        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
+        <v>楽しく学ぶ！フレイル対策講座</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>健康・医療・福祉</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C17" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
       </c>
       <c r="E17" t="str">
-        <v>こどもホスピス支援事業</v>
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
       </c>
     </row>
     <row r="18">
@@ -3877,7 +3905,7 @@
         <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C18" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D18" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016555/1037469.html</v>
@@ -3897,10 +3925,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
       </c>
       <c r="E19" t="str">
-        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
       </c>
     </row>
   </sheetData>
@@ -3912,7 +3940,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M207"/>
+  <dimension ref="A1:M229"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8393,9 +8421,503 @@
         <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
       </c>
     </row>
+    <row r="208">
+      <c r="B208" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C208" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D208" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F208" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G208" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H208" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C209" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D209" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+      </c>
+      <c r="F209" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G209" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H209" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C210" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D210" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+      </c>
+      <c r="F210" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G210" t="str">
+        <v>高齢者肺炎球菌(定期予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H210" t="str">
+        <v>高齢者肺炎球菌予防接種(定期予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C211" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D211" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="F211" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+      <c r="G211" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H211" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C212" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I212" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K212" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L212" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
+      </c>
+      <c r="M212" t="str">
+        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C213" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I213" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K213" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L213" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053423.html</v>
+      </c>
+      <c r="M213" t="str">
+        <v>令和8年度名古屋市交通安全実施計画</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C214" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I214" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K214" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L214" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
+      </c>
+      <c r="M214" t="str">
+        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C215" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I215" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K215" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L215" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
+      </c>
+      <c r="M215" t="str">
+        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C216" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I216" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K216" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L216" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
+      </c>
+      <c r="M216" t="str">
+        <v>愛知県勤労者スポーツフェスティバル</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C217" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I217" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K217" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L217" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
+      </c>
+      <c r="M217" t="str">
+        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C218" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I218" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K218" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L218" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
+      </c>
+      <c r="M218" t="str">
+        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C219" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I219" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K219" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L219" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
+      </c>
+      <c r="M219" t="str">
+        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C220" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I220" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K220" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L220" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
+      </c>
+      <c r="M220" t="str">
+        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C221" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I221" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J221" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K221" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L221" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1053964.html</v>
+      </c>
+      <c r="M221" t="str">
+        <v>こども性暴力防止法</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C222" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I222" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J222" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K222" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L222" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
+      </c>
+      <c r="M222" t="str">
+        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C223" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I223" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J223" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K223" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L223" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
+      </c>
+      <c r="M223" t="str">
+        <v>令和8年度 教育委員会9月定例会</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C224" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I224" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J224" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K224" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L224" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
+      </c>
+      <c r="M224" t="str">
+        <v>内山保育園の改築について</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C225" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I225" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J225" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K225" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L225" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
+      </c>
+      <c r="M225" t="str">
+        <v>公立保育所等の整備</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C226" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I226" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J226" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K226" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L226" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
+      </c>
+      <c r="M226" t="str">
+        <v>楽しく学ぶ！フレイル対策講座</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C227" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I227" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J227" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K227" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L227" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="M227" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C228" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I228" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J228" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K228" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L228" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016555/1037469.html</v>
+      </c>
+      <c r="M228" t="str">
+        <v>令和8年度アディクション・セッション「だれでもなる依存症 ーそれぞれの回復メッセージー」</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C229" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I229" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J229" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K229" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L229" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
+      </c>
+      <c r="M229" t="str">
+        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M229"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -3525,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3555,58 +3555,16 @@
         <v>data/services.js</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
-      </c>
-      <c r="B3" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C3" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D3" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
-      </c>
-      <c r="B4" t="str">
-        <v>高齢者肺炎球菌(定期予防接種)｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C4" t="str">
-        <v>高齢者肺炎球菌予防接種(定期予防接種)｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D4" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
-      </c>
-      <c r="B5" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C5" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D5" t="str">
-        <v>screens/DisasterScreen.js</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3636,10 +3594,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
       </c>
       <c r="E2" t="str">
-        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
+        <v>届出書類（東消防署）</v>
       </c>
     </row>
     <row r="3">
@@ -3653,10 +3611,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053423.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
       </c>
       <c r="E3" t="str">
-        <v>令和8年度名古屋市交通安全実施計画</v>
+        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
       </c>
     </row>
     <row r="4">
@@ -3670,10 +3628,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
       </c>
       <c r="E4" t="str">
-        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
+        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
       </c>
     </row>
     <row r="5">
@@ -3687,10 +3645,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
       </c>
       <c r="E5" t="str">
-        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
+        <v>中央卸売市場本場 親子体験イベント</v>
       </c>
     </row>
     <row r="6">
@@ -3704,10 +3662,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
       </c>
       <c r="E6" t="str">
-        <v>愛知県勤労者スポーツフェスティバル</v>
+        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
       </c>
     </row>
     <row r="7">
@@ -3721,10 +3679,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034809/1053714.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
       </c>
       <c r="E7" t="str">
-        <v>第47回生物多様性カフェ「目指せカエル博士！カエルトーク＆体験学習」</v>
+        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
       </c>
     </row>
     <row r="8">
@@ -3738,10 +3696,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014573/1053830.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
       </c>
       <c r="E8" t="str">
-        <v>令和8年9月8日の大雨により被害を受けられた方の住宅の応急修理について</v>
+        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
       </c>
     </row>
     <row r="9">
@@ -3755,10 +3713,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1053624.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
       </c>
       <c r="E9" t="str">
-        <v>富山県令和8年8月大雨災害義援金の募集について（富山県共同募金会）</v>
+        <v>愛知県勤労者スポーツフェスティバル</v>
       </c>
     </row>
     <row r="10">
@@ -3772,10 +3730,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
       </c>
       <c r="E10" t="str">
-        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
+        <v>令和8年度 教育委員会10月定例会</v>
       </c>
     </row>
     <row r="11">
@@ -3789,10 +3747,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/jisedai/1053964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
       </c>
       <c r="E11" t="str">
-        <v>こども性暴力防止法</v>
+        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="12">
@@ -3806,10 +3764,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
       </c>
       <c r="E12" t="str">
-        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="13">
@@ -3823,10 +3781,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1053692.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
       </c>
       <c r="E13" t="str">
-        <v>令和8年度 教育委員会9月定例会</v>
+        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
       </c>
     </row>
     <row r="14">
@@ -3840,107 +3798,22 @@
         <v>➖ 削除</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/1053872.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
       </c>
       <c r="E14" t="str">
-        <v>内山保育園の改築について</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C15" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1053829/index.html</v>
-      </c>
-      <c r="E15" t="str">
-        <v>公立保育所等の整備</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C16" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
-      </c>
-      <c r="E16" t="str">
-        <v>楽しく学ぶ！フレイル対策講座</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C17" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
-      </c>
-      <c r="E17" t="str">
-        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C18" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016555/1037469.html</v>
-      </c>
-      <c r="E18" t="str">
-        <v>令和8年度アディクション・セッション「だれでもなる依存症 ーそれぞれの回復メッセージー」</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C19" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
-      </c>
-      <c r="E19" t="str">
-        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
+        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:M243"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8915,9 +8788,328 @@
         <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
       </c>
     </row>
+    <row r="230">
+      <c r="B230" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C230" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D230" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F230" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G230" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H230" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C231" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I231" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J231" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K231" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L231" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
+      </c>
+      <c r="M231" t="str">
+        <v>届出書類（東消防署）</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C232" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I232" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J232" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K232" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L232" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
+      </c>
+      <c r="M232" t="str">
+        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C233" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I233" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J233" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K233" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L233" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
+      </c>
+      <c r="M233" t="str">
+        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C234" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I234" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J234" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K234" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L234" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
+      </c>
+      <c r="M234" t="str">
+        <v>中央卸売市場本場 親子体験イベント</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C235" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I235" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J235" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K235" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L235" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
+      </c>
+      <c r="M235" t="str">
+        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C236" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I236" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J236" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K236" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L236" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
+      </c>
+      <c r="M236" t="str">
+        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C237" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I237" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J237" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K237" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L237" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
+      </c>
+      <c r="M237" t="str">
+        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C238" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I238" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J238" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K238" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L238" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
+      </c>
+      <c r="M238" t="str">
+        <v>愛知県勤労者スポーツフェスティバル</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C239" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I239" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J239" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K239" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L239" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
+      </c>
+      <c r="M239" t="str">
+        <v>令和8年度 教育委員会10月定例会</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C240" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I240" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J240" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K240" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L240" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
+      </c>
+      <c r="M240" t="str">
+        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C241" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I241" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J241" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K241" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L241" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M241" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C242" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I242" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J242" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K242" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L242" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
+      </c>
+      <c r="M242" t="str">
+        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="C243" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I243" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J243" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K243" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L243" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
+      </c>
+      <c r="M243" t="str">
+        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M229"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M243"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -3525,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3555,16 +3555,30 @@
         <v>data/services.js</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+      </c>
+      <c r="B3" t="str">
+        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C3" t="str">
+        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D3" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3594,10 +3608,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
       </c>
       <c r="E2" t="str">
-        <v>届出書類（東消防署）</v>
+        <v>家具転倒防止ボランティアを派遣します！</v>
       </c>
     </row>
     <row r="3">
@@ -3608,81 +3622,81 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
       </c>
       <c r="E3" t="str">
-        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
+        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C4" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
       </c>
       <c r="E4" t="str">
-        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
+        <v>空き家対策に関する相談会等のお知らせ</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
       </c>
       <c r="E5" t="str">
-        <v>中央卸売市場本場 親子体験イベント</v>
+        <v>届出書類（東消防署）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C6" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
       </c>
       <c r="E6" t="str">
-        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
+        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C7" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034790/1054061.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
       </c>
       <c r="E7" t="str">
-        <v>令和8年度秋なごやの苗購入者キャンペーン</v>
+        <v>第12次名古屋市交通安全計画</v>
       </c>
     </row>
     <row r="8">
@@ -3693,13 +3707,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1034836/1040728/1052624.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
       </c>
       <c r="E8" t="str">
-        <v>ガイドヘルパー養成研修のご案内（令和8年10月18日開始分）</v>
+        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
       </c>
     </row>
     <row r="9">
@@ -3710,81 +3724,81 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C9" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016713/1054112.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
       </c>
       <c r="E9" t="str">
-        <v>愛知県勤労者スポーツフェスティバル</v>
+        <v>希少疾患講演会</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C10" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
       </c>
       <c r="E10" t="str">
-        <v>令和8年度 教育委員会10月定例会</v>
+        <v>水環境を学ぶイベント</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C12" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
       </c>
       <c r="E12" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>中央卸売市場本場 親子体験イベント</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C13" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1034352/1016778/1040312.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
       </c>
       <c r="E13" t="str">
-        <v>「名古屋市立中学校標準服について」のページを更新しました。</v>
+        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
       </c>
     </row>
     <row r="14">
@@ -3795,25 +3809,195 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C14" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1053644.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
       </c>
       <c r="E14" t="str">
-        <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
+        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C15" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
+      </c>
+      <c r="E15" t="str">
+        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C16" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D16" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
+      </c>
+      <c r="E16" t="str">
+        <v>令和8年度 教育委員会10月定例会</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C17" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D17" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
+      </c>
+      <c r="E17" t="str">
+        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C18" t="str">
+        <v>🔁 変更</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1009365.html</v>
+      </c>
+      <c r="E18" t="str">
+        <v>【このイベントは終了しました】名古屋市主催！大規模婚活イベント「那古野de婚活2025」 → 名古屋de大規模婚活2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C19" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
+      </c>
+      <c r="E19" t="str">
+        <v>あいち高次脳機能障害リハビリテーション講習会</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C20" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
+      </c>
+      <c r="E20" t="str">
+        <v>うつ病家族教室</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C21" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
+      </c>
+      <c r="E21" t="str">
+        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B22" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C22" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D22" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
+      </c>
+      <c r="E22" t="str">
+        <v>楽しく学ぶ！フレイル対策講座</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B23" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C23" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D23" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+      </c>
+      <c r="E23" t="str">
+        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B24" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C24" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D24" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="E24" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9107,9 +9291,578 @@
         <v>本地丘小学校・森孝東小学校・森孝西小学校の統合及び森孝中学校との併設に向けた説明会のご案内</v>
       </c>
     </row>
+    <row r="244">
+      <c r="B244" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C244" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D244" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F244" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G244" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H244" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C245" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D245" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+      </c>
+      <c r="F245" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G245" t="str">
+        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H245" t="str">
+        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C246" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I246" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J246" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K246" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L246" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
+      </c>
+      <c r="M246" t="str">
+        <v>家具転倒防止ボランティアを派遣します！</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C247" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I247" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J247" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K247" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L247" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
+      </c>
+      <c r="M247" t="str">
+        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C248" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I248" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J248" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K248" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L248" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
+      </c>
+      <c r="M248" t="str">
+        <v>空き家対策に関する相談会等のお知らせ</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C249" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I249" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J249" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K249" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L249" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
+      </c>
+      <c r="M249" t="str">
+        <v>届出書類（東消防署）</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C250" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I250" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J250" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K250" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L250" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
+      </c>
+      <c r="M250" t="str">
+        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C251" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I251" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J251" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K251" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L251" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
+      </c>
+      <c r="M251" t="str">
+        <v>第12次名古屋市交通安全計画</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C252" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I252" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J252" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K252" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L252" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
+      </c>
+      <c r="M252" t="str">
+        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C253" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I253" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J253" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K253" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L253" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
+      </c>
+      <c r="M253" t="str">
+        <v>希少疾患講演会</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C254" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I254" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J254" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K254" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L254" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
+      </c>
+      <c r="M254" t="str">
+        <v>水環境を学ぶイベント</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C255" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I255" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J255" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K255" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L255" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
+      </c>
+      <c r="M255" t="str">
+        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C256" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I256" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J256" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K256" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L256" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
+      </c>
+      <c r="M256" t="str">
+        <v>中央卸売市場本場 親子体験イベント</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C257" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I257" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J257" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K257" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L257" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
+      </c>
+      <c r="M257" t="str">
+        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C258" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I258" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J258" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K258" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L258" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
+      </c>
+      <c r="M258" t="str">
+        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C259" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I259" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J259" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K259" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L259" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
+      </c>
+      <c r="M259" t="str">
+        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C260" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I260" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J260" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K260" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L260" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
+      </c>
+      <c r="M260" t="str">
+        <v>令和8年度 教育委員会10月定例会</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C261" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I261" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J261" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K261" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L261" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
+      </c>
+      <c r="M261" t="str">
+        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C262" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I262" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J262" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K262" t="str">
+        <v>🔁 変更</v>
+      </c>
+      <c r="L262" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1009365.html</v>
+      </c>
+      <c r="M262" t="str">
+        <v>【このイベントは終了しました】名古屋市主催！大規模婚活イベント「那古野de婚活2025」 → 名古屋de大規模婚活2026</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C263" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I263" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J263" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K263" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L263" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
+      </c>
+      <c r="M263" t="str">
+        <v>あいち高次脳機能障害リハビリテーション講習会</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C264" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I264" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J264" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K264" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L264" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
+      </c>
+      <c r="M264" t="str">
+        <v>うつ病家族教室</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C265" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I265" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J265" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K265" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L265" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
+      </c>
+      <c r="M265" t="str">
+        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C266" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I266" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J266" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K266" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L266" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
+      </c>
+      <c r="M266" t="str">
+        <v>楽しく学ぶ！フレイル対策講座</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C267" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I267" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J267" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K267" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L267" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+      </c>
+      <c r="M267" t="str">
+        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="C268" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I268" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J268" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K268" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L268" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="M268" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M243"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M268"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -396,16 +396,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://script.google.com/macros/s/AKfycbzFCaaWabD78GxAySMPYeOkL38dx4Hpr4GuCCpl8VWtjy1aJHcChbRXqz8EGe-vWO4/exec</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="D2" t="str">
-        <v>data/districts.js</v>
+        <v>components/FeedbackForm.js</v>
       </c>
     </row>
     <row r="3">
@@ -413,13 +413,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="4">
@@ -427,13 +427,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -455,7 +455,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,7 +483,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C91">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,10 +1659,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C92">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D92" t="str">
         <v>data/services.js</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,7 +1911,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C110">
         <v>200</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
+        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C150">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C151">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2499,7 +2499,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C152">
         <v>200</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,7 +2541,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C155">
         <v>200</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,7 +2583,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C158">
         <v>200</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,13 +2611,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C160">
         <v>200</v>
       </c>
       <c r="D160" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="161">
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,7 +2639,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C162">
         <v>200</v>
@@ -2653,7 +2653,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C163">
         <v>200</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,7 +2821,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C175">
         <v>200</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://nagoyalink.net/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
+        <v>https://nagoyalink.net/</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,7 +3059,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://nagosapo.icds.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
       </c>
       <c r="C192">
         <v>200</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
+        <v>https://nagosapo.icds.jp/</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,7 +3087,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>https://maejob.icds.jp/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
       </c>
       <c r="C194">
         <v>200</v>
@@ -3101,7 +3101,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
+        <v>https://maejob.icds.jp/index.html</v>
       </c>
       <c r="C195">
         <v>200</v>
@@ -3115,7 +3115,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
       </c>
       <c r="C196">
         <v>200</v>
@@ -3129,7 +3129,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
       </c>
       <c r="C197">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
       </c>
       <c r="C198">
         <v>200</v>
@@ -3157,7 +3157,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B199" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
       </c>
       <c r="C199">
         <v>200</v>
@@ -3171,7 +3171,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B200" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
       </c>
       <c r="C200">
         <v>200</v>
@@ -3185,7 +3185,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B201" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
       </c>
       <c r="C201">
         <v>200</v>
@@ -3199,7 +3199,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B202" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
       </c>
       <c r="C202">
         <v>200</v>
@@ -3213,7 +3213,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B203" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
       </c>
       <c r="C203">
         <v>200</v>
@@ -3227,7 +3227,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B204" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
       </c>
       <c r="C204">
         <v>200</v>
@@ -3241,7 +3241,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B205" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
       </c>
       <c r="C205">
         <v>200</v>
@@ -3255,7 +3255,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B206" t="str">
-        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
       </c>
       <c r="C206">
         <v>200</v>
@@ -3269,7 +3269,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B207" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
+        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
       </c>
       <c r="C207">
         <v>200</v>
@@ -3283,7 +3283,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B208" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
       </c>
       <c r="C208">
         <v>200</v>
@@ -3297,7 +3297,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B209" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
       </c>
       <c r="C209">
         <v>200</v>
@@ -3311,7 +3311,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B210" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
       </c>
       <c r="C210">
         <v>200</v>
@@ -3325,7 +3325,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B211" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
       </c>
       <c r="C211">
         <v>200</v>
@@ -3339,7 +3339,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B212" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
       </c>
       <c r="C212">
         <v>200</v>
@@ -3353,7 +3353,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B213" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
       </c>
       <c r="C213">
         <v>200</v>
@@ -3367,7 +3367,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B214" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
       </c>
       <c r="C214">
         <v>200</v>
@@ -3381,7 +3381,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B215" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
       </c>
       <c r="C215">
         <v>200</v>
@@ -3395,7 +3395,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B216" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
       </c>
       <c r="C216">
         <v>200</v>
@@ -3409,7 +3409,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B217" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
       </c>
       <c r="C217">
         <v>200</v>
@@ -3423,7 +3423,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B218" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
       </c>
       <c r="C218">
         <v>200</v>
@@ -3437,7 +3437,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B219" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
       </c>
       <c r="C219">
         <v>200</v>
@@ -3451,7 +3451,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B220" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
       </c>
       <c r="C220">
         <v>200</v>
@@ -3465,13 +3465,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B221" t="str">
-        <v>https://www.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
       </c>
       <c r="C221">
         <v>200</v>
       </c>
       <c r="D221" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="222">
@@ -3479,7 +3479,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B222" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+        <v>https://www.city.nagoya.jp/</v>
       </c>
       <c r="C222">
         <v>200</v>
@@ -3493,13 +3493,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B223" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
       </c>
       <c r="C223">
         <v>200</v>
       </c>
       <c r="D223" t="str">
-        <v>screens/DisasterScreen.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="224">
@@ -3507,7 +3507,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B224" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
       </c>
       <c r="C224">
         <v>200</v>
@@ -3516,16 +3516,30 @@
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B225" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
+      </c>
+      <c r="C225">
+        <v>200</v>
+      </c>
+      <c r="D225" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D225"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3543,13 +3557,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="B2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3557,21 +3571,105 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="B3" t="str">
-        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C3" t="str">
-        <v>精神科救急情報センター｜名古屋市公式ウェブサイト</v>
+        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D3" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="B4" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="C4" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="D4" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+      </c>
+      <c r="B5" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C5" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D5" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+      </c>
+      <c r="B6" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="C6" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="D6" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="C7" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="D7" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+      </c>
+      <c r="B8" t="str">
+        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C8" t="str">
+        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D8" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+      </c>
+      <c r="B9" t="str">
+        <v>令和8年度ひとり親家庭等への大学受験料等補助｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C9" t="str">
+        <v>令和8年度ひとり親家庭等への大学受験料・模試費用補助｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D9" t="str">
         <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3608,10 +3706,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014468/1054839.html</v>
       </c>
       <c r="E2" t="str">
-        <v>家具転倒防止ボランティアを派遣します！</v>
+        <v>AIカメラ等を活用した客引き行為等対策の実証実験について</v>
       </c>
     </row>
     <row r="3">
@@ -3625,10 +3723,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1054663.html</v>
       </c>
       <c r="E3" t="str">
-        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
+        <v>防火わくわくフェス開催！</v>
       </c>
     </row>
     <row r="4">
@@ -3642,10 +3740,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1013208/1034498/1013209/1013224/1054826/index.html</v>
       </c>
       <c r="E4" t="str">
-        <v>空き家対策に関する相談会等のお知らせ</v>
+        <v>喫煙等禁止行為の解除</v>
       </c>
     </row>
     <row r="5">
@@ -3659,10 +3757,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012783/1053698/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
       </c>
       <c r="E5" t="str">
-        <v>届出書類（東消防署）</v>
+        <v>家具転倒防止ボランティアを派遣します！</v>
       </c>
     </row>
     <row r="6">
@@ -3676,10 +3774,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052498.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
       </c>
       <c r="E6" t="str">
-        <v>親子で楽しく学ぶ防災『親と子の災害体験教室』を開催しました</v>
+        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
       </c>
     </row>
     <row r="7">
@@ -3693,10 +3791,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014355/1014388/1053467.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
       </c>
       <c r="E7" t="str">
-        <v>第12次名古屋市交通安全計画</v>
+        <v>空き家対策に関する相談会等のお知らせ</v>
       </c>
     </row>
     <row r="8">
@@ -3710,10 +3808,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054819.html</v>
       </c>
       <c r="E8" t="str">
-        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
+        <v>名古屋シーライフ水族館とのコラボワークショップ「プラスチックごみから海をまもろう」</v>
       </c>
     </row>
     <row r="9">
@@ -3727,10 +3825,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052446.html</v>
       </c>
       <c r="E9" t="str">
-        <v>希少疾患講演会</v>
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」介助犬といっしょに学ぼう！ 間近で見て・体験する特別な一日</v>
       </c>
     </row>
     <row r="10">
@@ -3744,10 +3842,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1054583.html</v>
       </c>
       <c r="E10" t="str">
-        <v>水環境を学ぶイベント</v>
+        <v>草木類や木製家具等の木材は、木材再利用工場への搬入にご協力ください！</v>
       </c>
     </row>
     <row r="11">
@@ -3761,10 +3859,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012539/1016073/1035720/1052642.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
       </c>
       <c r="E11" t="str">
-        <v>名古屋市環境科学調査センター オープンラボ2026を開催します</v>
+        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
       </c>
     </row>
     <row r="12">
@@ -3778,10 +3876,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051952.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
       </c>
       <c r="E12" t="str">
-        <v>中央卸売市場本場 親子体験イベント</v>
+        <v>希少疾患講演会</v>
       </c>
     </row>
     <row r="13">
@@ -3795,10 +3893,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054167.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
       </c>
       <c r="E13" t="str">
-        <v>芸術と科学の杜 サイエンス＆アートフェスティバル</v>
+        <v>水環境を学ぶイベント</v>
       </c>
     </row>
     <row r="14">
@@ -3812,10 +3910,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1054337.html</v>
       </c>
       <c r="E14" t="str">
-        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年10月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="15">
@@ -3829,10 +3927,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054827.html</v>
       </c>
       <c r="E15" t="str">
-        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
+        <v>令和8年度 教育委員会10月臨時会（10月30日開催）</v>
       </c>
     </row>
     <row r="16">
@@ -3843,13 +3941,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C16" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054165.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1054366.html</v>
       </c>
       <c r="E16" t="str">
-        <v>令和8年度 教育委員会10月定例会</v>
+        <v>名古屋市×WEラブ赤ちゃんプロジェクト</v>
       </c>
     </row>
     <row r="17">
@@ -3863,10 +3961,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052683.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
       </c>
       <c r="E17" t="str">
-        <v>令和8年9月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="18">
@@ -3877,13 +3975,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C18" t="str">
-        <v>🔁 変更</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1009365.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
       </c>
       <c r="E18" t="str">
-        <v>【このイベントは終了しました】名古屋市主催！大規模婚活イベント「那古野de婚活2025」 → 名古屋de大規模婚活2026</v>
+        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
       </c>
     </row>
     <row r="19">
@@ -3897,10 +3995,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1052087.html</v>
       </c>
       <c r="E19" t="str">
-        <v>あいち高次脳機能障害リハビリテーション講習会</v>
+        <v>【あいち県民の日学校ホリデー】「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（親子向け・令和8年11月27日開催）</v>
       </c>
     </row>
     <row r="20">
@@ -3914,10 +4012,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1051395.html</v>
       </c>
       <c r="E20" t="str">
-        <v>うつ病家族教室</v>
+        <v>「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（高校生以上向け・令和8年11月26日開催）</v>
       </c>
     </row>
     <row r="21">
@@ -3931,10 +4029,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054783.html</v>
       </c>
       <c r="E21" t="str">
-        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
+        <v>TEACCHプログラム研究会愛知支部主催講演会のご案内</v>
       </c>
     </row>
     <row r="22">
@@ -3948,10 +4046,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D22" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1052650.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
       </c>
       <c r="E22" t="str">
-        <v>楽しく学ぶ！フレイル対策講座</v>
+        <v>あいち高次脳機能障害リハビリテーション講習会</v>
       </c>
     </row>
     <row r="23">
@@ -3965,10 +4063,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D23" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
       </c>
       <c r="E23" t="str">
-        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
+        <v>うつ病家族教室</v>
       </c>
     </row>
     <row r="24">
@@ -3982,10 +4080,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D24" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
       </c>
       <c r="E24" t="str">
-        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
       </c>
     </row>
   </sheetData>
@@ -3997,7 +4095,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M268"/>
+  <dimension ref="A1:M300"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9860,9 +9958,715 @@
         <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
       </c>
     </row>
+    <row r="269">
+      <c r="B269" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C269" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D269" t="str">
+        <v>https://script.google.com/macros/s/AKfycbzFCaaWabD78GxAySMPYeOkL38dx4Hpr4GuCCpl8VWtjy1aJHcChbRXqz8EGe-vWO4/exec</v>
+      </c>
+      <c r="E269">
+        <v>403</v>
+      </c>
+      <c r="F269" t="str">
+        <v>components/FeedbackForm.js</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C270" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D270" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+      </c>
+      <c r="F270" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G270" t="str">
+        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H270" t="str">
+        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C271" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D271" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+      </c>
+      <c r="F271" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G271" t="str">
+        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H271" t="str">
+        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C272" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D272" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F272" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G272" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H272" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C273" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D273" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+      </c>
+      <c r="F273" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G273" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H273" t="str">
+        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C274" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D274" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+      </c>
+      <c r="F274" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G274" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="H274" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C275" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D275" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+      </c>
+      <c r="F275" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G275" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="H275" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C276" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D276" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+      </c>
+      <c r="F276" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G276" t="str">
+        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H276" t="str">
+        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C277" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D277" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+      </c>
+      <c r="F277" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G277" t="str">
+        <v>令和8年度ひとり親家庭等への大学受験料等補助｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H277" t="str">
+        <v>令和8年度ひとり親家庭等への大学受験料・模試費用補助｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C278" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I278" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J278" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K278" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L278" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014468/1054839.html</v>
+      </c>
+      <c r="M278" t="str">
+        <v>AIカメラ等を活用した客引き行為等対策の実証実験について</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C279" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I279" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J279" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K279" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L279" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1054663.html</v>
+      </c>
+      <c r="M279" t="str">
+        <v>防火わくわくフェス開催！</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C280" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I280" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J280" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K280" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L280" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1013208/1034498/1013209/1013224/1054826/index.html</v>
+      </c>
+      <c r="M280" t="str">
+        <v>喫煙等禁止行為の解除</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C281" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I281" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J281" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K281" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L281" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
+      </c>
+      <c r="M281" t="str">
+        <v>家具転倒防止ボランティアを派遣します！</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C282" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I282" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J282" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K282" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L282" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
+      </c>
+      <c r="M282" t="str">
+        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C283" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I283" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J283" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K283" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L283" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
+      </c>
+      <c r="M283" t="str">
+        <v>空き家対策に関する相談会等のお知らせ</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C284" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I284" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J284" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K284" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L284" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054819.html</v>
+      </c>
+      <c r="M284" t="str">
+        <v>名古屋シーライフ水族館とのコラボワークショップ「プラスチックごみから海をまもろう」</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C285" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I285" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J285" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K285" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L285" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052446.html</v>
+      </c>
+      <c r="M285" t="str">
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」介助犬といっしょに学ぼう！ 間近で見て・体験する特別な一日</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C286" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I286" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J286" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K286" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L286" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1054583.html</v>
+      </c>
+      <c r="M286" t="str">
+        <v>草木類や木製家具等の木材は、木材再利用工場への搬入にご協力ください！</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C287" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I287" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J287" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K287" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L287" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
+      </c>
+      <c r="M287" t="str">
+        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C288" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I288" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J288" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K288" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L288" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
+      </c>
+      <c r="M288" t="str">
+        <v>希少疾患講演会</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C289" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I289" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J289" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K289" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L289" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
+      </c>
+      <c r="M289" t="str">
+        <v>水環境を学ぶイベント</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C290" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I290" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J290" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K290" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L290" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1054337.html</v>
+      </c>
+      <c r="M290" t="str">
+        <v>令和8年10月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C291" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I291" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J291" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K291" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L291" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054827.html</v>
+      </c>
+      <c r="M291" t="str">
+        <v>令和8年度 教育委員会10月臨時会（10月30日開催）</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C292" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I292" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J292" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K292" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L292" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1054366.html</v>
+      </c>
+      <c r="M292" t="str">
+        <v>名古屋市×WEラブ赤ちゃんプロジェクト</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C293" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I293" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J293" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K293" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L293" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
+      </c>
+      <c r="M293" t="str">
+        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C294" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I294" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J294" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K294" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L294" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
+      </c>
+      <c r="M294" t="str">
+        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C295" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I295" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J295" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K295" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L295" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1052087.html</v>
+      </c>
+      <c r="M295" t="str">
+        <v>【あいち県民の日学校ホリデー】「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（親子向け・令和8年11月27日開催）</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C296" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I296" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J296" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K296" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L296" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1051395.html</v>
+      </c>
+      <c r="M296" t="str">
+        <v>「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（高校生以上向け・令和8年11月26日開催）</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C297" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I297" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J297" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K297" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L297" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054783.html</v>
+      </c>
+      <c r="M297" t="str">
+        <v>TEACCHプログラム研究会愛知支部主催講演会のご案内</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C298" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I298" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J298" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K298" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L298" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
+      </c>
+      <c r="M298" t="str">
+        <v>あいち高次脳機能障害リハビリテーション講習会</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C299" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I299" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J299" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K299" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L299" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
+      </c>
+      <c r="M299" t="str">
+        <v>うつ病家族教室</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C300" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I300" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J300" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K300" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L300" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
+      </c>
+      <c r="M300" t="str">
+        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M268"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M300"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -3539,7 +3539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3557,545 +3557,49 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="B2" t="str">
-        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
+        <v>幼児教育・保育の無償化について｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C2" t="str">
-        <v>なごやジョブサポートセンター｜名古屋市公式ウェブサイト</v>
+        <v>幼児教育・保育の無償化について｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D2" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
-      </c>
-      <c r="B3" t="str">
-        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C3" t="str">
-        <v>高齢者就業に関する施設｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D3" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>https://www.bes-c.com/</v>
-      </c>
-      <c r="B4" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
-      </c>
-      <c r="C4" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
-      </c>
-      <c r="D4" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
-      </c>
-      <c r="B5" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C5" t="str">
-        <v>なごや子ども応援委員会｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D5" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
-      </c>
-      <c r="B6" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="C6" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="D6" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="C7" t="str">
-        <v>高校生等への修学支援：文部科学省</v>
-      </c>
-      <c r="D7" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
-      </c>
-      <c r="B8" t="str">
-        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C8" t="str">
-        <v>名古屋市奨学金（高等学校給付型奨学金）｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D8" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
-      </c>
-      <c r="B9" t="str">
-        <v>令和8年度ひとり親家庭等への大学受験料等補助｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C9" t="str">
-        <v>令和8年度ひとり親家庭等への大学受験料・模試費用補助｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D9" t="str">
         <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>タブ</v>
-      </c>
-      <c r="B1" t="str">
-        <v>タブURL</v>
-      </c>
-      <c r="C1" t="str">
-        <v>種別</v>
-      </c>
-      <c r="D1" t="str">
-        <v>対象URL</v>
-      </c>
-      <c r="E1" t="str">
-        <v>内容</v>
+        <v>状態</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C2" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014468/1054839.html</v>
-      </c>
-      <c r="E2" t="str">
-        <v>AIカメラ等を活用した客引き行為等対策の実証実験について</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C3" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1054663.html</v>
-      </c>
-      <c r="E3" t="str">
-        <v>防火わくわくフェス開催！</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C4" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1013208/1034498/1013209/1013224/1054826/index.html</v>
-      </c>
-      <c r="E4" t="str">
-        <v>喫煙等禁止行為の解除</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C5" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1053749/index.html</v>
-      </c>
-      <c r="E5" t="str">
-        <v>家具転倒防止ボランティアを派遣します！</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C6" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1054380.html</v>
-      </c>
-      <c r="E6" t="str">
-        <v>令和8年8月、救急隊員への感謝を込めて寄贈いただきました</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C7" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1014554.html</v>
-      </c>
-      <c r="E7" t="str">
-        <v>空き家対策に関する相談会等のお知らせ</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C8" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1054819.html</v>
-      </c>
-      <c r="E8" t="str">
-        <v>名古屋シーライフ水族館とのコラボワークショップ「プラスチックごみから海をまもろう」</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C9" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052446.html</v>
-      </c>
-      <c r="E9" t="str">
-        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」介助犬といっしょに学ぼう！ 間近で見て・体験する特別な一日</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C10" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1054583.html</v>
-      </c>
-      <c r="E10" t="str">
-        <v>草木類や木製家具等の木材は、木材再利用工場への搬入にご協力ください！</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C11" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1037173/1016131/1034822/1016141/1034825/1046051/1054545.html</v>
-      </c>
-      <c r="E11" t="str">
-        <v>令和8年9月 名古屋市中央卸売市場月別取扱高</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C12" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1053603.html</v>
-      </c>
-      <c r="E12" t="str">
-        <v>希少疾患講演会</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C13" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012555/1054510/index.html</v>
-      </c>
-      <c r="E13" t="str">
-        <v>水環境を学ぶイベント</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C14" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1054337.html</v>
-      </c>
-      <c r="E14" t="str">
-        <v>令和8年10月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C15" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1054827.html</v>
-      </c>
-      <c r="E15" t="str">
-        <v>令和8年度 教育委員会10月臨時会（10月30日開催）</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C16" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kodomomirai/1054366.html</v>
-      </c>
-      <c r="E16" t="str">
-        <v>名古屋市×WEラブ赤ちゃんプロジェクト</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C17" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1053895.html</v>
-      </c>
-      <c r="E17" t="str">
-        <v>令和8年10月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C18" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1009080/1041843.html</v>
-      </c>
-      <c r="E18" t="str">
-        <v>子ども会活動アシストバンク事業の内容を幅広く知っていただくため、子ども向けの体験イベントと保護者向けの事業説明を兼ねたワークショップを開催します。</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C19" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1052087.html</v>
-      </c>
-      <c r="E19" t="str">
-        <v>【あいち県民の日学校ホリデー】「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（親子向け・令和8年11月27日開催）</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C20" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015429/1051395.html</v>
-      </c>
-      <c r="E20" t="str">
-        <v>「見える！感じる！DNA」（食品安全・安心学習センター）参加者を募集します（高校生以上向け・令和8年11月26日開催）</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C21" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054783.html</v>
-      </c>
-      <c r="E21" t="str">
-        <v>TEACCHプログラム研究会愛知支部主催講演会のご案内</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C22" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D22" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1054316.html</v>
-      </c>
-      <c r="E22" t="str">
-        <v>あいち高次脳機能障害リハビリテーション講習会</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C23" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D23" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1054374.html</v>
-      </c>
-      <c r="E23" t="str">
-        <v>うつ病家族教室</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C24" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D24" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1048759/1054411.html</v>
-      </c>
-      <c r="E24" t="str">
-        <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
+        <v>検知なし</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M300"/>
+  <dimension ref="A1:M302"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10664,9 +10168,46 @@
         <v>愛知県自閉症協会・つぼみの会セミナーのご案内</v>
       </c>
     </row>
+    <row r="301">
+      <c r="B301" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C301" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D301" t="str">
+        <v>https://script.google.com/macros/s/AKfycbzFCaaWabD78GxAySMPYeOkL38dx4Hpr4GuCCpl8VWtjy1aJHcChbRXqz8EGe-vWO4/exec</v>
+      </c>
+      <c r="E301">
+        <v>403</v>
+      </c>
+      <c r="F301" t="str">
+        <v>components/FeedbackForm.js</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C302" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D302" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+      </c>
+      <c r="F302" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G302" t="str">
+        <v>幼児教育・保育の無償化について｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H302" t="str">
+        <v>幼児教育・保育の無償化について｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M300"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M302"/>
   </ignoredErrors>
 </worksheet>
 </file>